--- a/data/trans_dic/P21_R-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P21_R-Edad-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha utilizado un servicio de urgencias en el último año</t>
+          <t>Población que ha utilizado un servicio de urgencias en el último año (tasa de respuesta: 99,88%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>16,64; 23,88</t>
+          <t>16,21; 23,69</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>20,14; 28,2</t>
+          <t>20,48; 28,3</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>18,22; 26,22</t>
+          <t>18,06; 26,76</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>12,25; 26,65</t>
+          <t>12,18; 27,71</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>20,17; 28,39</t>
+          <t>20,43; 27,45</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>25,81; 34,68</t>
+          <t>25,51; 34,81</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>19,73; 28,11</t>
+          <t>19,52; 28,23</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>19,99; 33,76</t>
+          <t>19,38; 32,96</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>19,29; 24,57</t>
+          <t>19,44; 24,42</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>24,06; 29,84</t>
+          <t>23,82; 30,12</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>20,31; 26,19</t>
+          <t>20,42; 26,26</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>17,35; 27,51</t>
+          <t>17,31; 27,57</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>12,8; 18,23</t>
+          <t>12,58; 17,86</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>20,44; 26,78</t>
+          <t>20,51; 27,16</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>13,46; 19,96</t>
+          <t>13,34; 19,52</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>16,23; 26,43</t>
+          <t>16,11; 26,16</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>25,71; 33,54</t>
+          <t>26,0; 33,41</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>31,28; 39,08</t>
+          <t>31,4; 39,55</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>21,4; 28,73</t>
+          <t>21,34; 28,6</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>14,6; 29,52</t>
+          <t>15,22; 29,64</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>19,66; 24,15</t>
+          <t>19,5; 24,04</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>26,73; 31,53</t>
+          <t>26,42; 31,49</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>18,34; 23,23</t>
+          <t>18,1; 23,19</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>16,54; 26,29</t>
+          <t>17,08; 26,14</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>11,39; 17,3</t>
+          <t>11,54; 17,16</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>15,47; 21,48</t>
+          <t>15,48; 21,75</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>13,45; 19,12</t>
+          <t>13,54; 19,52</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>18,54; 25,84</t>
+          <t>18,57; 25,76</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>16,85; 23,31</t>
+          <t>16,85; 22,71</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>20,81; 27,03</t>
+          <t>20,83; 27,6</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>18,37; 24,66</t>
+          <t>18,78; 24,78</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>21,14; 27,39</t>
+          <t>21,53; 27,57</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>15,07; 19,29</t>
+          <t>15,13; 19,38</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>18,88; 23,6</t>
+          <t>19,17; 23,76</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>16,67; 20,97</t>
+          <t>16,72; 21,11</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>20,58; 25,56</t>
+          <t>20,82; 25,73</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>12,51; 19,36</t>
+          <t>12,64; 18,91</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>13,34; 19,32</t>
+          <t>13,31; 19,31</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>11,31; 17,13</t>
+          <t>11,45; 17,13</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>7,49; 25,67</t>
+          <t>7,23; 25,84</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>16,92; 24,02</t>
+          <t>16,7; 23,78</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>17,59; 24,57</t>
+          <t>17,72; 24,9</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>14,98; 21,22</t>
+          <t>14,98; 21,2</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>18,96; 25,35</t>
+          <t>19,31; 25,52</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>15,5; 20,26</t>
+          <t>15,16; 20,11</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>16,39; 21,09</t>
+          <t>16,28; 21,02</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>14,02; 18,31</t>
+          <t>14,07; 18,49</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>11,39; 24,43</t>
+          <t>11,44; 24,36</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>12,65; 20,32</t>
+          <t>12,77; 20,22</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>14,14; 21,66</t>
+          <t>14,05; 21,7</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>12,27; 19,24</t>
+          <t>12,34; 18,8</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>17,42; 23,65</t>
+          <t>17,45; 23,64</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>17,36; 25,52</t>
+          <t>17,88; 25,44</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>19,67; 27,35</t>
+          <t>19,32; 27,59</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>14,68; 21,86</t>
+          <t>14,77; 22,15</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>21,45; 26,84</t>
+          <t>21,22; 26,67</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>16,19; 21,94</t>
+          <t>16,1; 22,1</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>17,88; 23,4</t>
+          <t>17,51; 23,15</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>14,25; 19,31</t>
+          <t>14,52; 19,59</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>20,29; 24,34</t>
+          <t>20,14; 24,47</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>16,05; 25,33</t>
+          <t>16,86; 25,88</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>13,37; 23,19</t>
+          <t>13,94; 23,86</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>12,95; 21,34</t>
+          <t>13,21; 21,55</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>14,14; 20,68</t>
+          <t>14,2; 20,7</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>22,73; 32,41</t>
+          <t>23,56; 32,72</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>21,29; 30,54</t>
+          <t>21,67; 31,53</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>16,95; 25,66</t>
+          <t>17,27; 26,25</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>21,76; 78,36</t>
+          <t>21,75; 75,13</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>21,29; 27,76</t>
+          <t>21,54; 27,86</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>19,21; 25,94</t>
+          <t>19,07; 25,72</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>16,35; 22,3</t>
+          <t>16,42; 22,48</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>19,45; 65,39</t>
+          <t>19,54; 66,0</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>21,3; 32,88</t>
+          <t>21,01; 33,77</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>24,94; 38,22</t>
+          <t>24,59; 36,92</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>13,88; 22,27</t>
+          <t>13,44; 22,39</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>17,17; 24,63</t>
+          <t>16,83; 24,22</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>26,37; 36,94</t>
+          <t>26,34; 37,07</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>32,06; 42,14</t>
+          <t>31,72; 41,28</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>20,1; 30,06</t>
+          <t>20,11; 29,91</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>25,55; 32,04</t>
+          <t>25,83; 31,86</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>25,76; 34,35</t>
+          <t>25,72; 33,75</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>30,63; 38,22</t>
+          <t>30,86; 38,69</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>18,58; 25,42</t>
+          <t>18,47; 25,63</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>23,18; 28,17</t>
+          <t>23,05; 27,91</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>15,91; 18,54</t>
+          <t>15,73; 18,4</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>19,24; 22,17</t>
+          <t>19,3; 22,15</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>15,33; 17,98</t>
+          <t>15,4; 17,89</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>15,24; 21,67</t>
+          <t>15,17; 21,86</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>22,94; 25,86</t>
+          <t>22,94; 25,84</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>26,08; 29,2</t>
+          <t>26,13; 29,33</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>20,07; 22,89</t>
+          <t>20,19; 23,1</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>23,87; 43,22</t>
+          <t>23,92; 42,03</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>19,81; 21,78</t>
+          <t>19,83; 21,8</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>23,15; 25,26</t>
+          <t>23,13; 25,28</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>18,17; 20,13</t>
+          <t>18,16; 20,11</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>21,15; 32,19</t>
+          <t>21,47; 32,67</t>
         </is>
       </c>
     </row>
@@ -1810,7 +1810,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha utilizado un servicio de urgencias en el último año</t>
+          <t>Población que ha utilizado un servicio de urgencias en el último año (tasa de respuesta: 99,88%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2068,62 +2068,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>82220; 117964</t>
+          <t>80104; 117020</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>91258; 127818</t>
+          <t>92812; 128253</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>76425; 109990</t>
+          <t>75758; 112250</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>49000; 106591</t>
+          <t>48727; 110819</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>94095; 132472</t>
+          <t>95313; 128064</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>111045; 149196</t>
+          <t>109773; 149749</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>78095; 111239</t>
+          <t>77246; 111739</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>62177; 104990</t>
+          <t>60265; 102507</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>185266; 236059</t>
+          <t>186753; 234556</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>212546; 263633</t>
+          <t>210436; 266115</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>165576; 213475</t>
+          <t>166434; 214114</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>123353; 195573</t>
+          <t>123080; 196000</t>
         </is>
       </c>
     </row>
@@ -2276,62 +2276,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>94138; 134091</t>
+          <t>92549; 131353</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>140458; 184019</t>
+          <t>140935; 186611</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>79043; 117222</t>
+          <t>78363; 114630</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>68721; 111963</t>
+          <t>68253; 110814</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>160810; 209798</t>
+          <t>162625; 208996</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>190569; 238091</t>
+          <t>191318; 240973</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>120428; 161634</t>
+          <t>120073; 160943</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>74664; 151006</t>
+          <t>77830; 151623</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>267627; 328668</t>
+          <t>265330; 327163</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>346563; 408708</t>
+          <t>342565; 408251</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>210954; 267079</t>
+          <t>208094; 266653</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>154682; 245864</t>
+          <t>159680; 244425</t>
         </is>
       </c>
     </row>
@@ -2484,62 +2484,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>72650; 110315</t>
+          <t>73625; 109469</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>105399; 146287</t>
+          <t>105464; 148163</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>89659; 127425</t>
+          <t>90282; 130091</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>99442; 138584</t>
+          <t>99594; 138147</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>116236; 160787</t>
+          <t>116219; 156631</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>147684; 191810</t>
+          <t>147817; 195835</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>121358; 162903</t>
+          <t>124038; 163647</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>114316; 148144</t>
+          <t>116432; 149124</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>200106; 256045</t>
+          <t>200867; 257335</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>262626; 328225</t>
+          <t>266597; 330498</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>221157; 278222</t>
+          <t>221865; 280118</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>221673; 275385</t>
+          <t>224284; 277147</t>
         </is>
       </c>
     </row>
@@ -2692,62 +2692,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>64969; 100528</t>
+          <t>65597; 98175</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>81987; 118734</t>
+          <t>81820; 118710</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>72866; 110303</t>
+          <t>73743; 110299</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>66370; 227468</t>
+          <t>64060; 228936</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>87228; 123839</t>
+          <t>86125; 122618</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>108223; 151166</t>
+          <t>108998; 153180</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>97225; 137743</t>
+          <t>97200; 137615</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>135021; 180579</t>
+          <t>137532; 181728</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>160357; 209623</t>
+          <t>156925; 208123</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>201598; 259372</t>
+          <t>200264; 258556</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>181286; 236758</t>
+          <t>181933; 239056</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>182081; 390532</t>
+          <t>182796; 389377</t>
         </is>
       </c>
     </row>
@@ -2900,62 +2900,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>48930; 78566</t>
+          <t>49383; 78178</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>60716; 93002</t>
+          <t>60342; 93200</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>58423; 91577</t>
+          <t>58714; 89471</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>97793; 132723</t>
+          <t>97915; 132673</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>70135; 103099</t>
+          <t>72235; 102769</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>88080; 122463</t>
+          <t>86521; 123561</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>72662; 108207</t>
+          <t>73130; 109664</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>117014; 146432</t>
+          <t>115764; 145508</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>127984; 173452</t>
+          <t>127272; 174708</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>156874; 205267</t>
+          <t>153622; 203119</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>138386; 187488</t>
+          <t>141031; 190189</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>224615; 269437</t>
+          <t>222863; 270785</t>
         </is>
       </c>
     </row>
@@ -3108,62 +3108,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>46950; 74107</t>
+          <t>49318; 75724</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>41289; 71616</t>
+          <t>43051; 73665</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>43170; 71148</t>
+          <t>44026; 71844</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>52055; 76141</t>
+          <t>52278; 76203</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>77962; 111139</t>
+          <t>80799; 112201</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>75380; 108097</t>
+          <t>76710; 111620</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>63739; 96515</t>
+          <t>64974; 98735</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>132252; 476270</t>
+          <t>132223; 456634</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>135280; 176449</t>
+          <t>136916; 177051</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>127316; 171934</t>
+          <t>126363; 170467</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>116017; 158192</t>
+          <t>116518; 159494</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>189796; 638198</t>
+          <t>190718; 644090</t>
         </is>
       </c>
     </row>
@@ -3316,62 +3316,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>44696; 69012</t>
+          <t>44093; 70887</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>62313; 95496</t>
+          <t>61443; 92249</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>35679; 57230</t>
+          <t>34537; 57544</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>48539; 69651</t>
+          <t>47593; 68475</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>88064; 123350</t>
+          <t>87937; 123787</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>124724; 163907</t>
+          <t>123389; 160588</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>80182; 119895</t>
+          <t>80201; 119330</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>108533; 136097</t>
+          <t>109716; 135341</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>140074; 186776</t>
+          <t>139845; 183528</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>195655; 244154</t>
+          <t>197124; 247137</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>121848; 166735</t>
+          <t>121168; 168099</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>163974; 199317</t>
+          <t>163054; 197476</t>
         </is>
       </c>
     </row>
@@ -3524,62 +3524,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>521268; 607385</t>
+          <t>515224; 602739</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>658662; 759263</t>
+          <t>660984; 758293</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>518647; 608351</t>
+          <t>521233; 605503</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>527034; 749197</t>
+          <t>524524; 755954</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>774989; 873724</t>
+          <t>774864; 872861</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>927222; 1038189</t>
+          <t>928969; 1042891</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>710011; 809947</t>
+          <t>714275; 817333</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>871974; 1578998</t>
+          <t>873901; 1535499</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>1317955; 1449133</t>
+          <t>1319432; 1450792</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>1615706; 1763105</t>
+          <t>1614116; 1764599</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>1257784; 1393367</t>
+          <t>1256781; 1391939</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>1504178; 2288957</t>
+          <t>1526592; 2323565</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P21_R-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P21_R-Edad-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>18,97%</t>
+          <t>18,06%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>26,17%</t>
+          <t>26,38%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>22,12%</t>
+          <t>21,96%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>16,21; 23,69</t>
+          <t>16,32; 23,73</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>20,48; 28,3</t>
+          <t>20,27; 28,47</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>18,06; 26,76</t>
+          <t>17,89; 26,71</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>12,18; 27,71</t>
+          <t>12,81; 26,25</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>20,43; 27,45</t>
+          <t>20,21; 27,67</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>25,51; 34,81</t>
+          <t>25,84; 34,68</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>19,52; 28,23</t>
+          <t>19,86; 28,65</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>19,38; 32,96</t>
+          <t>20,22; 33,06</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>19,44; 24,42</t>
+          <t>19,32; 24,62</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>23,82; 30,12</t>
+          <t>24,09; 30,0</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>20,42; 26,26</t>
+          <t>20,03; 26,0</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>17,31; 27,57</t>
+          <t>17,84; 26,5</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>20,84%</t>
+          <t>20,44%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>24,0%</t>
+          <t>26,05%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>22,57%</t>
+          <t>23,31%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>12,58; 17,86</t>
+          <t>12,66; 17,95</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>20,51; 27,16</t>
+          <t>20,39; 27,21</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>13,34; 19,52</t>
+          <t>13,62; 19,89</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>16,11; 26,16</t>
+          <t>15,69; 25,63</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>26,0; 33,41</t>
+          <t>25,86; 33,54</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>31,4; 39,55</t>
+          <t>30,96; 38,92</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>21,34; 28,6</t>
+          <t>21,55; 28,76</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>15,22; 29,64</t>
+          <t>21,61; 30,1</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>19,5; 24,04</t>
+          <t>19,69; 24,31</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>26,42; 31,49</t>
+          <t>26,1; 31,41</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>18,1; 23,19</t>
+          <t>18,23; 23,05</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>17,08; 26,14</t>
+          <t>20,55; 27,16</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>21,88%</t>
+          <t>20,72%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>24,14%</t>
+          <t>24,33%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>23,01%</t>
+          <t>22,52%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>11,54; 17,16</t>
+          <t>11,21; 17,0</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>15,48; 21,75</t>
+          <t>15,53; 21,86</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>13,54; 19,52</t>
+          <t>13,43; 19,23</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>18,57; 25,76</t>
+          <t>17,69; 24,41</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>16,85; 22,71</t>
+          <t>16,93; 23,04</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>20,83; 27,6</t>
+          <t>20,81; 27,48</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>18,78; 24,78</t>
+          <t>18,44; 24,7</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>21,53; 27,57</t>
+          <t>21,61; 27,42</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>15,13; 19,38</t>
+          <t>15,11; 19,27</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>19,17; 23,76</t>
+          <t>18,84; 23,74</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>16,72; 21,11</t>
+          <t>16,75; 21,13</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>20,82; 25,73</t>
+          <t>20,33; 24,93</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>17,85%</t>
+          <t>24,8%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>22,75%</t>
+          <t>24,0%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>20,04%</t>
+          <t>24,39%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>12,64; 18,91</t>
+          <t>12,52; 19,35</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>13,31; 19,31</t>
+          <t>13,42; 19,39</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>11,45; 17,13</t>
+          <t>11,36; 17,21</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>7,23; 25,84</t>
+          <t>21,8; 28,4</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>16,7; 23,78</t>
+          <t>16,95; 23,71</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>17,72; 24,9</t>
+          <t>17,46; 24,7</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>14,98; 21,2</t>
+          <t>15,13; 21,21</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>19,31; 25,52</t>
+          <t>21,68; 26,6</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>15,16; 20,11</t>
+          <t>15,47; 20,16</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>16,28; 21,02</t>
+          <t>16,35; 21,22</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>14,07; 18,49</t>
+          <t>14,13; 18,45</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>11,44; 24,36</t>
+          <t>22,37; 26,68</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>20,54%</t>
+          <t>20,51%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>23,99%</t>
+          <t>24,14%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>22,24%</t>
+          <t>22,32%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>12,77; 20,22</t>
+          <t>12,93; 20,2</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>14,05; 21,7</t>
+          <t>13,96; 21,44</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>12,34; 18,8</t>
+          <t>12,05; 18,97</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>17,45; 23,64</t>
+          <t>17,73; 24,0</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>17,88; 25,44</t>
+          <t>17,38; 25,74</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>19,32; 27,59</t>
+          <t>19,09; 27,33</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>14,77; 22,15</t>
+          <t>14,73; 22,13</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>21,22; 26,67</t>
+          <t>21,53; 26,9</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>16,1; 22,1</t>
+          <t>16,36; 21,89</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>17,51; 23,15</t>
+          <t>17,83; 23,09</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>14,52; 19,59</t>
+          <t>14,36; 19,51</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>20,14; 24,47</t>
+          <t>20,29; 24,39</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>17,4%</t>
+          <t>17,66%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>48,79%</t>
+          <t>23,29%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>36,95%</t>
+          <t>20,58%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>16,86; 25,88</t>
+          <t>16,57; 25,96</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>13,94; 23,86</t>
+          <t>13,93; 22,97</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>13,21; 21,55</t>
+          <t>13,14; 21,85</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>14,2; 20,7</t>
+          <t>15,0; 21,19</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>23,56; 32,72</t>
+          <t>22,81; 32,55</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>21,67; 31,53</t>
+          <t>21,39; 30,87</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>17,27; 26,25</t>
+          <t>17,39; 26,06</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>21,75; 75,13</t>
+          <t>20,4; 26,29</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>21,54; 27,86</t>
+          <t>20,79; 27,59</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>19,07; 25,72</t>
+          <t>19,4; 26,14</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>16,42; 22,48</t>
+          <t>16,39; 22,44</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>19,54; 66,0</t>
+          <t>18,44; 22,82</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>20,49%</t>
+          <t>20,41%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>28,8%</t>
+          <t>28,62%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>25,48%</t>
+          <t>25,33%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>21,01; 33,77</t>
+          <t>21,38; 33,14</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>24,59; 36,92</t>
+          <t>24,59; 37,55</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>13,44; 22,39</t>
+          <t>13,67; 22,72</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>16,83; 24,22</t>
+          <t>17,09; 24,78</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>26,34; 37,07</t>
+          <t>26,23; 36,73</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>31,72; 41,28</t>
+          <t>31,69; 41,6</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>20,11; 29,91</t>
+          <t>20,11; 29,25</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>25,83; 31,86</t>
+          <t>25,67; 31,95</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>25,72; 33,75</t>
+          <t>25,79; 33,62</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>30,86; 38,69</t>
+          <t>30,42; 38,5</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>18,47; 25,63</t>
+          <t>18,5; 25,47</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>23,05; 27,91</t>
+          <t>22,8; 27,8</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>19,58%</t>
+          <t>20,77%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>28,64%</t>
+          <t>25,07%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>24,23%</t>
+          <t>22,98%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>15,73; 18,4</t>
+          <t>15,89; 18,49</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>19,3; 22,15</t>
+          <t>19,09; 22,01</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>15,4; 17,89</t>
+          <t>15,53; 18,05</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>15,17; 21,86</t>
+          <t>19,27; 22,28</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>22,94; 25,84</t>
+          <t>22,88; 25,74</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>26,13; 29,33</t>
+          <t>26,2; 29,26</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>20,19; 23,1</t>
+          <t>20,17; 23,0</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>23,92; 42,03</t>
+          <t>23,84; 26,26</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>19,83; 21,8</t>
+          <t>19,78; 21,85</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>23,13; 25,28</t>
+          <t>23,18; 25,29</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>18,16; 20,11</t>
+          <t>18,27; 20,22</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>21,47; 32,67</t>
+          <t>22,02; 24,01</t>
         </is>
       </c>
     </row>
@@ -2015,7 +2015,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>75878</t>
+          <t>73657</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2035,7 +2035,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>81389</t>
+          <t>95039</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2055,7 +2055,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>157267</t>
+          <t>168695</t>
         </is>
       </c>
     </row>
@@ -2068,62 +2068,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>80104; 117020</t>
+          <t>80619; 117236</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>92812; 128253</t>
+          <t>91857; 129039</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>75758; 112250</t>
+          <t>75036; 112040</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>48727; 110819</t>
+          <t>52243; 107061</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>95313; 128064</t>
+          <t>94277; 129115</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>109773; 149749</t>
+          <t>111157; 149199</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>77246; 111739</t>
+          <t>78586; 113401</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>60265; 102507</t>
+          <t>72863; 119117</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>186753; 234556</t>
+          <t>185613; 236467</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>210436; 266115</t>
+          <t>212774; 264985</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>166434; 214114</t>
+          <t>163307; 211946</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>123080; 196000</t>
+          <t>137000; 203519</t>
         </is>
       </c>
     </row>
@@ -2223,7 +2223,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>88270</t>
+          <t>97465</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2243,7 +2243,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>122761</t>
+          <t>130520</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2263,7 +2263,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>211031</t>
+          <t>227986</t>
         </is>
       </c>
     </row>
@@ -2276,62 +2276,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>92549; 131353</t>
+          <t>93131; 132053</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>140935; 186611</t>
+          <t>140096; 186964</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>78363; 114630</t>
+          <t>80014; 116815</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>68253; 110814</t>
+          <t>74834; 122231</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>162625; 208996</t>
+          <t>161726; 209801</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>191318; 240973</t>
+          <t>188606; 237108</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>120073; 160943</t>
+          <t>121233; 161807</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>77830; 151623</t>
+          <t>108266; 150827</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>265330; 327163</t>
+          <t>267936; 330792</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>342565; 408251</t>
+          <t>338293; 407159</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>208094; 266653</t>
+          <t>209598; 265069</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>159680; 244425</t>
+          <t>200927; 265613</t>
         </is>
       </c>
     </row>
@@ -2431,7 +2431,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>117344</t>
+          <t>128613</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2451,7 +2451,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>130548</t>
+          <t>150967</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>247891</t>
+          <t>279580</t>
         </is>
       </c>
     </row>
@@ -2484,62 +2484,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>73625; 109469</t>
+          <t>71512; 108437</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>105464; 148163</t>
+          <t>105767; 148885</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>90282; 130091</t>
+          <t>89485; 128201</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>99594; 138147</t>
+          <t>109818; 151549</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>116219; 156631</t>
+          <t>116773; 158932</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>147817; 195835</t>
+          <t>147684; 195003</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>124038; 163647</t>
+          <t>121821; 163156</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>116432; 149124</t>
+          <t>134067; 170177</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>200867; 257335</t>
+          <t>200565; 255838</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>266597; 330498</t>
+          <t>262097; 330152</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>221865; 280118</t>
+          <t>222270; 280347</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>224284; 277147</t>
+          <t>252359; 309479</t>
         </is>
       </c>
     </row>
@@ -2639,7 +2639,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>158175</t>
+          <t>173286</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2659,7 +2659,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>162048</t>
+          <t>176673</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2679,7 +2679,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>320223</t>
+          <t>349959</t>
         </is>
       </c>
     </row>
@@ -2692,62 +2692,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>65597; 98175</t>
+          <t>64972; 100438</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>81820; 118710</t>
+          <t>82498; 119165</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>73743; 110299</t>
+          <t>73149; 110814</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>64060; 228936</t>
+          <t>152326; 198420</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>86125; 122618</t>
+          <t>87380; 122259</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>108998; 153180</t>
+          <t>107421; 151959</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>97200; 137615</t>
+          <t>98206; 137699</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>137532; 181728</t>
+          <t>159578; 195837</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>156925; 208123</t>
+          <t>160058; 208624</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>200264; 258556</t>
+          <t>201122; 260968</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>181933; 239056</t>
+          <t>182778; 238542</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>182796; 389377</t>
+          <t>321012; 382786</t>
         </is>
       </c>
     </row>
@@ -2847,7 +2847,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>115273</t>
+          <t>124955</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2867,7 +2867,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>130899</t>
+          <t>146779</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2887,7 +2887,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>246172</t>
+          <t>271734</t>
         </is>
       </c>
     </row>
@@ -2900,62 +2900,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>49383; 78178</t>
+          <t>50000; 78116</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>60342; 93200</t>
+          <t>59967; 92070</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>58714; 89471</t>
+          <t>57350; 90308</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>97915; 132673</t>
+          <t>108062; 146219</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>72235; 102769</t>
+          <t>70206; 103979</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>86521; 123561</t>
+          <t>85472; 122373</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>73130; 109664</t>
+          <t>72920; 109555</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>115764; 145508</t>
+          <t>130919; 163576</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>127272; 174708</t>
+          <t>129347; 173090</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>153622; 203119</t>
+          <t>156452; 202566</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>141031; 190189</t>
+          <t>139428; 189441</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>222863; 270785</t>
+          <t>247056; 296933</t>
         </is>
       </c>
     </row>
@@ -3055,7 +3055,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>64042</t>
+          <t>71884</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3075,7 +3075,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>296532</t>
+          <t>102126</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3095,7 +3095,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>360574</t>
+          <t>174010</t>
         </is>
       </c>
     </row>
@@ -3108,62 +3108,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>49318; 75724</t>
+          <t>48468; 75946</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>43051; 73665</t>
+          <t>43003; 70942</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>44026; 71844</t>
+          <t>43806; 72832</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>52278; 76203</t>
+          <t>61061; 86249</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>80799; 112201</t>
+          <t>78217; 111633</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>76710; 111620</t>
+          <t>75714; 109272</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>64974; 98735</t>
+          <t>65417; 98010</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>132223; 456634</t>
+          <t>89463; 115280</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>136916; 177051</t>
+          <t>132107; 175351</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>126363; 170467</t>
+          <t>128549; 173258</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>116518; 159494</t>
+          <t>116272; 159243</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>190718; 644090</t>
+          <t>155951; 192945</t>
         </is>
       </c>
     </row>
@@ -3263,7 +3263,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>57941</t>
+          <t>63322</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3283,7 +3283,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>122310</t>
+          <t>132625</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3303,7 +3303,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>180251</t>
+          <t>195947</t>
         </is>
       </c>
     </row>
@@ -3316,62 +3316,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>44093; 70887</t>
+          <t>44883; 69548</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>61443; 92249</t>
+          <t>61427; 93815</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>34537; 57544</t>
+          <t>35140; 58379</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>47593; 68475</t>
+          <t>53021; 76882</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>87937; 123787</t>
+          <t>87594; 122654</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>123389; 160588</t>
+          <t>123266; 161809</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>80201; 119330</t>
+          <t>80199; 116697</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>109716; 135341</t>
+          <t>118953; 148069</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>139845; 183528</t>
+          <t>140257; 182837</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>197124; 247137</t>
+          <t>194347; 245948</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>121168; 168099</t>
+          <t>121353; 167025</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>163054; 197476</t>
+          <t>176384; 215046</t>
         </is>
       </c>
     </row>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>676924</t>
+          <t>733182</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3491,7 +3491,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>1046486</t>
+          <t>934729</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>1723411</t>
+          <t>1667911</t>
         </is>
       </c>
     </row>
@@ -3524,62 +3524,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>515224; 602739</t>
+          <t>520496; 605763</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>660984; 758293</t>
+          <t>653775; 753657</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>521233; 605503</t>
+          <t>525366; 610908</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>524524; 755954</t>
+          <t>680550; 786603</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>774864; 872861</t>
+          <t>772794; 869588</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>928969; 1042891</t>
+          <t>931378; 1040224</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>714275; 817333</t>
+          <t>713789; 813841</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>873901; 1535499</t>
+          <t>888878; 978948</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>1319432; 1450792</t>
+          <t>1316431; 1454107</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>1614116; 1764599</t>
+          <t>1617893; 1765029</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>1256781; 1391939</t>
+          <t>1264567; 1399609</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>1526592; 2323565</t>
+          <t>1598604; 1743154</t>
         </is>
       </c>
     </row>
